--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.17913114751985</v>
+        <v>4.254108811471976</v>
       </c>
       <c r="D2" t="n">
-        <v>26.2796400440787</v>
+        <v>4.270441507162789</v>
       </c>
       <c r="E2" t="n">
-        <v>15.86708555737889</v>
+        <v>2.57840140307407</v>
       </c>
       <c r="F2" t="n">
-        <v>15.80584946474143</v>
+        <v>2.568450538020483</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.68127004435145</v>
+        <v>4.498206382207111</v>
       </c>
       <c r="D3" t="n">
-        <v>27.58950851672688</v>
+        <v>4.483295133968118</v>
       </c>
       <c r="E3" t="n">
-        <v>15.86708555737889</v>
+        <v>2.57840140307407</v>
       </c>
       <c r="F3" t="n">
-        <v>15.80584946474143</v>
+        <v>2.568450538020483</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.56422358507994</v>
+        <v>9.841686332575492</v>
       </c>
       <c r="D4" t="n">
-        <v>60.4446493519029</v>
+        <v>9.822255519684223</v>
       </c>
       <c r="E4" t="n">
-        <v>15.86708555737889</v>
+        <v>2.57840140307407</v>
       </c>
       <c r="F4" t="n">
-        <v>15.80584946474143</v>
+        <v>2.568450538020483</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
